--- a/app/files/months.xlsx
+++ b/app/files/months.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -32,10 +32,46 @@
     <t xml:space="preserve">sport</t>
   </si>
   <si>
+    <t xml:space="preserve">Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nationality</t>
+  </si>
+  <si>
     <t xml:space="preserve">ian</t>
   </si>
   <si>
     <t xml:space="preserve">rugby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ragga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kenya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soccer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">muffin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">India</t>
   </si>
   <si>
     <t xml:space="preserve">Contextures Products</t>
@@ -349,33 +385,119 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>423720</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>243000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1695600</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>681120</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="Image 1" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="423720" y="243000"/>
+          <a:ext cx="1271880" cy="438120"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D1048576"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21.05"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1020" style="0" width="9.14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>1</v>
-      </c>
-    </row>
+    <row r="1" customFormat="false" ht="67.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="D2" s="0" t="s">
         <v>3</v>
       </c>
     </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -384,6 +506,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -393,7 +516,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultColWidth="8.859375" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.8515625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="41.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="64"/>
@@ -404,55 +527,55 @@
     <row r="1" customFormat="false" ht="6.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -460,39 +583,39 @@
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -500,15 +623,15 @@
     </row>
     <row r="16" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
